--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -644,34 +644,34 @@
         <v>4.44</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA2">
         <v>2.35</v>
@@ -680,19 +680,19 @@
         <v>1.51</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="O2">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="Q2">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T2">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U2">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.44</v>
@@ -674,19 +674,19 @@
         <v>2.7</v>
       </c>
       <c r="AA2">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB2">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AC2">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="AD2">
         <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
         <v>2.05</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
         <v>1.83</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -638,7 +638,7 @@
         <v>1.93</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
         <v>4.2</v>
@@ -650,10 +650,10 @@
         <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T2">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
         <v>3.4</v>
@@ -662,10 +662,10 @@
         <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y2">
         <v>1.44</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
         <v>1.83</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,46 +635,46 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
         <v>4.2</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="R2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S2">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U2">
         <v>3.4</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z2">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AA2">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB2">
         <v>1.58</v>
@@ -686,7 +686,7 @@
         <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
         <v>2.05</v>
@@ -801,10 +801,10 @@
         <v>3.1</v>
       </c>
       <c r="O3">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -644,22 +644,22 @@
         <v>4.2</v>
       </c>
       <c r="Q2">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
         <v>2.02</v>
       </c>
       <c r="S2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T2">
         <v>2.34</v>
       </c>
       <c r="U2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
         <v>1.02</v>
@@ -674,13 +674,13 @@
         <v>2.57</v>
       </c>
       <c r="AA2">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC2">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="AD2">
         <v>1.14</v>
@@ -689,7 +689,7 @@
         <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG2">
         <v>1.67</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
         <v>2.25</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
+        <v>3.05</v>
+      </c>
+      <c r="O3">
         <v>3.2</v>
       </c>
-      <c r="O3">
-        <v>3.3</v>
-      </c>
       <c r="P3">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O2">
         <v>3.3</v>
@@ -647,49 +647,49 @@
         <v>2.6</v>
       </c>
       <c r="R2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="U2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.45</v>
       </c>
       <c r="Z2">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB2">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AC2">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD2">
         <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG2">
         <v>1.67</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O2">
         <v>3.3</v>
       </c>
       <c r="P2">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S2">
         <v>1.52</v>
@@ -668,19 +668,19 @@
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z2">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA2">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AB2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD2">
         <v>1.14</v>
@@ -689,10 +689,10 @@
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK2">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>3.25</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -644,10 +644,10 @@
         <v>3.48</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.52</v>
@@ -659,19 +659,19 @@
         <v>3.6</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
         <v>1.48</v>
       </c>
       <c r="Z2">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AA2">
         <v>2.32</v>
@@ -680,13 +680,13 @@
         <v>1.52</v>
       </c>
       <c r="AC2">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AD2">
         <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
         <v>2.11</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>3.25</v>
       </c>
       <c r="O3">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="P2">
         <v>3.48</v>
@@ -662,34 +662,34 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>1.48</v>
       </c>
       <c r="Z2">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AA2">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AB2">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AC2">
         <v>4.65</v>
       </c>
       <c r="AD2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AG2">
         <v>1.65</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
+        <v>3.1</v>
+      </c>
+      <c r="O3">
         <v>3.25</v>
       </c>
-      <c r="O3">
-        <v>3.3</v>
-      </c>
       <c r="P3">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA3">
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
         <v>3.07</v>
       </c>
       <c r="P2">
-        <v>3.48</v>
+        <v>3.95</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -653,40 +653,40 @@
         <v>1.52</v>
       </c>
       <c r="T2">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="U2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V2">
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.48</v>
       </c>
       <c r="Z2">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AA2">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AB2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC2">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
         <v>2.13</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="O3">
         <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q3">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="R3">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
         <v>2.99</v>
@@ -828,19 +828,19 @@
         <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA3">
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC3">
         <v>3.54</v>
@@ -849,10 +849,10 @@
         <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG3">
         <v>1.88</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>3.95</v>
+        <v>3.48</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -656,13 +656,13 @@
         <v>2.35</v>
       </c>
       <c r="U2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="V2">
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X2">
         <v>1.06</v>
@@ -674,13 +674,13 @@
         <v>2.44</v>
       </c>
       <c r="AA2">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AB2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC2">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AD2">
         <v>1.14</v>
@@ -689,7 +689,7 @@
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AG2">
         <v>1.65</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>3.36</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P3">
         <v>2.25</v>
@@ -813,10 +813,10 @@
         <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
         <v>2.99</v>
@@ -831,7 +831,7 @@
         <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
         <v>3.1</v>
@@ -840,7 +840,7 @@
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC3">
         <v>3.54</v>
@@ -849,13 +849,13 @@
         <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-07-30.xlsx
+++ b/jogos_2026-07-30.xlsx
@@ -635,61 +635,61 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="P2">
         <v>3.48</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S2">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="T2">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.48</v>
       </c>
       <c r="Z2">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="AA2">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AB2">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AC2">
-        <v>4.65</v>
+        <v>5.39</v>
       </c>
       <c r="AD2">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AG2">
         <v>1.65</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="P3">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
         <v>1.03</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>3.54</v>
+        <v>3.92</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
+        <v>1.9</v>
+      </c>
+      <c r="AG3">
         <v>1.8</v>
       </c>
-      <c r="AG3">
-        <v>2</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL3">
         <v>0</v>
